--- a/Dataset/EN/xlsx/ITAMed_complete_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_complete_EN.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics; Infectious Diseases</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; General Surgery</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery; Oncology</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery; Oncology</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Pharmacology and Toxicology</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Oncology</t>
+          <t>Oncology; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pediatrics; General Surgery</t>
+          <t>Pediatrics; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Occupational Medicine</t>
+          <t>Infectious Diseases; Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Gastroenterology</t>
+          <t>Gastroenterology; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Internal Medicine</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Endocrinology; Nephrology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Anesthesia and Intensive Care</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Oncology; Gastroenterology</t>
+          <t>Gastroenterology; Oncology</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Oncology; Pharmacology and Toxicology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Oncology; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Endocrinology; Pediatrics</t>
+          <t>Pediatrics; Endocrinology</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Endocrinology; Pediatrics</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Pediatrics; Urology</t>
+          <t>Pediatrics; Nephrology</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Pediatrics; Urology</t>
+          <t>Pediatrics; Infectious Diseases</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Psychiatry; Pharmacology and Toxicology</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Urology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Urology; Pharmacology and Toxicology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care; Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Infectious Diseases</t>
+          <t>Infectious Diseases; Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Endocrinology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Hygiene, Epidemiology and Statistics; Forensic Medicine</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Nephrology</t>
+          <t>Nephrology; Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Pharmacology and Toxicology</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Endocrinology; Nephrology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Nephrology; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13605,7 +13605,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Pulmonology and Thoracic Surgery</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13721,7 +13721,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Nephrology; Endocrinology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14137,7 +14137,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Gynecology and Obstetrics</t>
+          <t>Dermatology and Venereology; Infectious Diseases</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Nephrology; Pharmacology and Toxicology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Nephrology; Immunology and Rheumatology</t>
+          <t>Immunology and Rheumatology; Nephrology</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Oncology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Ophthalmology; Pediatrics</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Oncology</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>General Surgery; Pediatrics</t>
+          <t>Otorhinolaryngology; Pediatrics</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -16197,7 +16197,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Oncology</t>
+          <t>Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Anesthesia and Intensive Care</t>
+          <t>Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -17241,7 +17241,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Forensic Medicine</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -17357,7 +17357,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Anesthesia and Intensive Care</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; General Surgery</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>General Surgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>Oncology; Gastroenterology</t>
+          <t>Gastroenterology; Oncology</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -18459,7 +18459,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; General Surgery</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Medical Genetics</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Pulmonology and Thoracic Surgery</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Hematology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Gastroenterology; Hematology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery</t>
+          <t>Infectious Diseases; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -21901,7 +21901,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Hematology; Gynecology and Obstetrics</t>
+          <t>Gynecology and Obstetrics; Hematology</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Infectious Diseases</t>
+          <t>Infectious Diseases; Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -22665,7 +22665,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
@@ -22781,7 +22781,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Pediatrics; Psychiatry</t>
+          <t>Pediatrics</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Oncology; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Pediatrics</t>
+          <t>Pediatrics; Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Pediatrics</t>
+          <t>Pediatrics; Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pediatrics</t>
+          <t>Pediatrics; Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -23951,7 +23951,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Medical Genetics; Pediatrics</t>
+          <t>Pediatrics; Medical Genetics</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -24009,7 +24009,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Nephrology; Pediatrics</t>
+          <t>Pediatrics; Nephrology</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -24067,7 +24067,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>Hematology; Pediatrics</t>
+          <t>Medical Genetics</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -24183,7 +24183,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Endocrinology; Pediatrics</t>
+          <t>Pediatrics; Endocrinology</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -24947,7 +24947,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Hygiene, Epidemiology and Statistics</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Cardiology and Cardiac Surgery</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -25585,7 +25585,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>Hematology; Pharmacology and Toxicology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
@@ -25875,7 +25875,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Hematology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L434" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>Urology; Pharmacology and Toxicology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -26165,7 +26165,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>Oncology; Orthopedics and Traumatology</t>
+          <t>Hematology; Pediatrics</t>
         </is>
       </c>
       <c r="L439" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; Infectious Diseases</t>
+          <t>Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -26455,7 +26455,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>Hematology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L444" t="inlineStr">
@@ -27219,7 +27219,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Pharmacology and Toxicology</t>
+          <t>Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Hematology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Ophthalmology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -28679,7 +28679,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Pediatrics; Oncology</t>
+          <t>Pediatrics; Hematology</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -28737,7 +28737,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>Hematology; Pediatrics</t>
+          <t>Pediatrics; Hematology</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -28911,7 +28911,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -29433,7 +29433,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>General Surgery; Anesthesia and Intensive Care</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -29549,7 +29549,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Endocrinology</t>
+          <t>Endocrinology; Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pharmacology and Toxicology</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -30787,7 +30787,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Medical Genetics; Otorhinolaryngology</t>
+          <t>Medical Genetics</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Otorhinolaryngology; Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L519" t="inlineStr">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Neurology and Neurosurgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -31367,7 +31367,7 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Infectious Diseases</t>
+          <t>Infectious Diseases; Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -31599,7 +31599,7 @@
       </c>
       <c r="K532" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Urology</t>
+          <t>Urology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -31657,7 +31657,7 @@
       </c>
       <c r="K533" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
@@ -31725,7 +31725,7 @@
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -31793,7 +31793,7 @@
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -32083,7 +32083,7 @@
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Nephrology; Pharmacology and Toxicology</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -32199,7 +32199,7 @@
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Nephrology</t>
+          <t>Nephrology; Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="K555" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Infectious Diseases</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L555" t="inlineStr">
@@ -33417,7 +33417,7 @@
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Gastroenterology</t>
+          <t>Gastroenterology; Infectious Diseases</t>
         </is>
       </c>
       <c r="L563" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="K575" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; General Surgery</t>
+          <t>Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L575" t="inlineStr">
@@ -34703,7 +34703,7 @@
       </c>
       <c r="K585" t="inlineStr">
         <is>
-          <t>Hematology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
@@ -34877,7 +34877,7 @@
       </c>
       <c r="K588" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
@@ -34993,7 +34993,7 @@
       </c>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Clinical Nutrition; Gastroenterology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>Medical Genetics; Oncology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L592" t="inlineStr">
@@ -35593,7 +35593,7 @@
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
@@ -35709,7 +35709,7 @@
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
@@ -36637,7 +36637,7 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Pediatrics</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
@@ -37333,7 +37333,7 @@
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
@@ -38029,7 +38029,7 @@
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Hygiene, Epidemiology and Statistics</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; Gynecology and Obstetrics</t>
+          <t>Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L643" t="inlineStr">
@@ -38261,7 +38261,7 @@
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -38493,7 +38493,7 @@
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>Urology; Oncology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -38667,7 +38667,7 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Ophthalmology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -39025,7 +39025,7 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Endocrinology</t>
+          <t>Otorhinolaryngology; General Surgery</t>
         </is>
       </c>
       <c r="L659" t="inlineStr">
@@ -39199,7 +39199,7 @@
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; General Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -39431,7 +39431,7 @@
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics; General Surgery</t>
         </is>
       </c>
       <c r="L666" t="inlineStr">
@@ -40205,7 +40205,7 @@
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Anesthesia and Intensive Care</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
@@ -40379,7 +40379,7 @@
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L682" t="inlineStr">
@@ -40611,7 +40611,7 @@
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Cardiology and Cardiac Surgery</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -40901,7 +40901,7 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L691" t="inlineStr">
@@ -40959,7 +40959,7 @@
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L692" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>Forensic Medicine; Hygiene, Epidemiology and Statistics</t>
+          <t>Hygiene, Epidemiology and Statistics; Forensic Medicine</t>
         </is>
       </c>
       <c r="L695" t="inlineStr">
@@ -41249,7 +41249,7 @@
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>Occupational Medicine; Oncology</t>
+          <t>Occupational Medicine</t>
         </is>
       </c>
       <c r="L697" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Occupational Medicine</t>
+          <t>Occupational Medicine; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L698" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>Forensic Medicine; Gynecology and Obstetrics</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="L700" t="inlineStr">
@@ -41713,7 +41713,7 @@
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Oncology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
@@ -43347,7 +43347,7 @@
       </c>
       <c r="K733" t="inlineStr">
         <is>
-          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L733" t="inlineStr">
@@ -43405,7 +43405,7 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>Oncology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Oncology</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -43811,7 +43811,7 @@
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L741" t="inlineStr">
@@ -44101,7 +44101,7 @@
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>Nephrology; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery; Nephrology</t>
         </is>
       </c>
       <c r="L746" t="inlineStr">
@@ -44275,7 +44275,7 @@
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Nephrology</t>
+          <t>Immunology and Rheumatology</t>
         </is>
       </c>
       <c r="L749" t="inlineStr">
@@ -44449,7 +44449,7 @@
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>Endocrinology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Endocrinology</t>
         </is>
       </c>
       <c r="L752" t="inlineStr">
@@ -44507,7 +44507,7 @@
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Medical Genetics</t>
+          <t>Neurology and Neurosurgery; Pediatrics</t>
         </is>
       </c>
       <c r="L753" t="inlineStr">
@@ -44681,7 +44681,7 @@
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>Pediatrics; General Surgery</t>
+          <t>General Surgery; Pediatrics</t>
         </is>
       </c>
       <c r="L756" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>Nephrology; Medical Genetics</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="L757" t="inlineStr">
@@ -45783,7 +45783,7 @@
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>General Surgery; Oncology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L775" t="inlineStr">
@@ -46373,7 +46373,7 @@
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
@@ -46799,7 +46799,7 @@
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L792" t="inlineStr">
@@ -47321,7 +47321,7 @@
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Neurology and Neurosurgery</t>
+          <t>Orthopedics and Traumatology; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L801" t="inlineStr">
@@ -47437,7 +47437,7 @@
       </c>
       <c r="K803" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L803" t="inlineStr">
@@ -47669,7 +47669,7 @@
       </c>
       <c r="K807" t="inlineStr">
         <is>
-          <t>Hematology; Oncology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L807" t="inlineStr">
@@ -47785,7 +47785,7 @@
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Immunology and Rheumatology</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Clinical Nutrition</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
@@ -48017,7 +48017,7 @@
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; General Surgery</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L813" t="inlineStr">
@@ -48249,7 +48249,7 @@
       </c>
       <c r="K817" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Forensic Medicine</t>
+          <t>Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L817" t="inlineStr">
@@ -48307,7 +48307,7 @@
       </c>
       <c r="K818" t="inlineStr">
         <is>
-          <t>Oncology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Oncology</t>
         </is>
       </c>
       <c r="L818" t="inlineStr">
@@ -48365,7 +48365,7 @@
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Immunology and Rheumatology</t>
+          <t>Anesthesia and Intensive Care; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L819" t="inlineStr">
@@ -48771,7 +48771,7 @@
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
@@ -48945,7 +48945,7 @@
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>Oncology; Medical Genetics</t>
+          <t>Medical Genetics; Oncology</t>
         </is>
       </c>
       <c r="L829" t="inlineStr">
@@ -49119,7 +49119,7 @@
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Cardiology and Cardiac Surgery</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
@@ -49293,7 +49293,7 @@
       </c>
       <c r="K835" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Infectious Diseases</t>
+          <t>Infectious Diseases; Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L835" t="inlineStr">
@@ -49351,7 +49351,7 @@
       </c>
       <c r="K836" t="inlineStr">
         <is>
-          <t>Hygiene, Epidemiology and Statistics; Infectious Diseases</t>
+          <t>Infectious Diseases; Hygiene, Epidemiology and Statistics</t>
         </is>
       </c>
       <c r="L836" t="inlineStr">
@@ -49409,7 +49409,7 @@
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t>Occupational Medicine; Pulmonology and Thoracic Surgery</t>
+          <t>Occupational Medicine</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
@@ -49989,7 +49989,7 @@
       </c>
       <c r="K847" t="inlineStr">
         <is>
-          <t>Medical Genetics; Oncology</t>
+          <t>Oncology; Medical Genetics</t>
         </is>
       </c>
       <c r="L847" t="inlineStr">
@@ -50163,7 +50163,7 @@
       </c>
       <c r="K850" t="inlineStr">
         <is>
-          <t>Ophthalmology; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Ophthalmology</t>
         </is>
       </c>
       <c r="L850" t="inlineStr">
@@ -50395,7 +50395,7 @@
       </c>
       <c r="K854" t="inlineStr">
         <is>
-          <t>General Surgery; Oncology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L854" t="inlineStr">
@@ -50453,7 +50453,7 @@
       </c>
       <c r="K855" t="inlineStr">
         <is>
-          <t>Endocrinology; Medical Genetics</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L855" t="inlineStr">
@@ -50937,7 +50937,7 @@
       </c>
       <c r="K863" t="inlineStr">
         <is>
-          <t>Gastroenterology; General Surgery</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L863" t="inlineStr">
@@ -51111,7 +51111,7 @@
       </c>
       <c r="K866" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Endocrinology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L866" t="inlineStr">
@@ -51691,7 +51691,7 @@
       </c>
       <c r="K876" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L876" t="inlineStr">
@@ -52445,7 +52445,7 @@
       </c>
       <c r="K889" t="inlineStr">
         <is>
-          <t>Pediatrics; Infectious Diseases</t>
+          <t>Infectious Diseases; Pediatrics</t>
         </is>
       </c>
       <c r="L889" t="inlineStr">
@@ -52629,7 +52629,7 @@
       </c>
       <c r="K892" t="inlineStr">
         <is>
-          <t>Dermatology and Venereology; Pharmacology and Toxicology</t>
+          <t>Pharmacology and Toxicology; Dermatology and Venereology</t>
         </is>
       </c>
       <c r="L892" t="inlineStr">
@@ -52881,7 +52881,7 @@
       </c>
       <c r="K896" t="inlineStr">
         <is>
-          <t>Endocrinology; Oncology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L896" t="inlineStr">
@@ -53171,7 +53171,7 @@
       </c>
       <c r="K901" t="inlineStr">
         <is>
-          <t>Psychiatry; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Psychiatry</t>
         </is>
       </c>
       <c r="L901" t="inlineStr">
@@ -53761,7 +53761,7 @@
       </c>
       <c r="K911" t="inlineStr">
         <is>
-          <t>Gastroenterology; Pharmacology and Toxicology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L911" t="inlineStr">
@@ -54051,7 +54051,7 @@
       </c>
       <c r="K916" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L916" t="inlineStr">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="K917" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Anesthesia and Intensive Care</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L917" t="inlineStr">
@@ -54167,7 +54167,7 @@
       </c>
       <c r="K918" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Pharmacology and Toxicology</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L918" t="inlineStr">
@@ -54815,7 +54815,7 @@
       </c>
       <c r="K929" t="inlineStr">
         <is>
-          <t>Oncology; Hematology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L929" t="inlineStr">
@@ -55569,7 +55569,7 @@
       </c>
       <c r="K942" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Psychiatry</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L942" t="inlineStr">
@@ -55859,7 +55859,7 @@
       </c>
       <c r="K947" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L947" t="inlineStr">
@@ -56179,7 +56179,7 @@
       </c>
       <c r="K952" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics; General Surgery</t>
         </is>
       </c>
       <c r="L952" t="inlineStr">
@@ -56353,7 +56353,7 @@
       </c>
       <c r="K955" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Infectious Diseases</t>
         </is>
       </c>
       <c r="L955" t="inlineStr">
@@ -56527,7 +56527,7 @@
       </c>
       <c r="K958" t="inlineStr">
         <is>
-          <t>Medical Genetics; Pediatrics</t>
+          <t>Pediatrics; Infectious Diseases</t>
         </is>
       </c>
       <c r="L958" t="inlineStr">
@@ -56701,7 +56701,7 @@
       </c>
       <c r="K961" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Hygiene, Epidemiology and Statistics; Forensic Medicine</t>
         </is>
       </c>
       <c r="L961" t="inlineStr">
@@ -56933,7 +56933,7 @@
       </c>
       <c r="K965" t="inlineStr">
         <is>
-          <t>Forensic Medicine; Pediatrics</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="L965" t="inlineStr">
@@ -57165,7 +57165,7 @@
       </c>
       <c r="K969" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Immunology and Rheumatology</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L969" t="inlineStr">
@@ -57339,7 +57339,7 @@
       </c>
       <c r="K972" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Urology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L972" t="inlineStr">
@@ -57523,7 +57523,7 @@
       </c>
       <c r="K975" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Pharmacology and Toxicology</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L975" t="inlineStr">
@@ -57581,7 +57581,7 @@
       </c>
       <c r="K976" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L976" t="inlineStr">
@@ -57697,7 +57697,7 @@
       </c>
       <c r="K978" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Pulmonology and Thoracic Surgery</t>
+          <t>Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L978" t="inlineStr">
@@ -58625,7 +58625,7 @@
       </c>
       <c r="K994" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Dermatology and Venereology; General Surgery</t>
         </is>
       </c>
       <c r="L994" t="inlineStr">
@@ -58799,7 +58799,7 @@
       </c>
       <c r="K997" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; General Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L997" t="inlineStr">
@@ -59089,7 +59089,7 @@
       </c>
       <c r="K1002" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L1002" t="inlineStr">
@@ -59147,7 +59147,7 @@
       </c>
       <c r="K1003" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L1003" t="inlineStr">
@@ -59611,7 +59611,7 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L1011" t="inlineStr">
@@ -59785,7 +59785,7 @@
       </c>
       <c r="K1014" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; General Surgery</t>
+          <t>General Surgery; Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L1014" t="inlineStr">
@@ -60075,7 +60075,7 @@
       </c>
       <c r="K1019" t="inlineStr">
         <is>
-          <t>Urology; Oncology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L1019" t="inlineStr">
@@ -60559,7 +60559,7 @@
       </c>
       <c r="K1027" t="inlineStr">
         <is>
-          <t>Nephrology; Hematology</t>
+          <t>Hematology; Nephrology</t>
         </is>
       </c>
       <c r="L1027" t="inlineStr">
@@ -60849,7 +60849,7 @@
       </c>
       <c r="K1032" t="inlineStr">
         <is>
-          <t>Gastroenterology; Hematology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L1032" t="inlineStr">
@@ -60965,7 +60965,7 @@
       </c>
       <c r="K1034" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L1034" t="inlineStr">
@@ -61081,7 +61081,7 @@
       </c>
       <c r="K1036" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pediatrics</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L1036" t="inlineStr">
@@ -61903,7 +61903,7 @@
       </c>
       <c r="K1050" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L1050" t="inlineStr">
@@ -62493,7 +62493,7 @@
       </c>
       <c r="K1060" t="inlineStr">
         <is>
-          <t>Pharmacology and Toxicology; Pulmonology and Thoracic Surgery</t>
+          <t>Pulmonology and Thoracic Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L1060" t="inlineStr">
@@ -63015,7 +63015,7 @@
       </c>
       <c r="K1069" t="inlineStr">
         <is>
-          <t>Urology; Oncology</t>
+          <t>Oncology; Urology</t>
         </is>
       </c>
       <c r="L1069" t="inlineStr">
@@ -63073,7 +63073,7 @@
       </c>
       <c r="K1070" t="inlineStr">
         <is>
-          <t>Oncology; Pharmacology and Toxicology</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L1070" t="inlineStr">
@@ -63131,7 +63131,7 @@
       </c>
       <c r="K1071" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Pediatrics</t>
+          <t>Ophthalmology; Pediatrics</t>
         </is>
       </c>
       <c r="L1071" t="inlineStr">
@@ -63363,7 +63363,7 @@
       </c>
       <c r="K1075" t="inlineStr">
         <is>
-          <t>Medical Genetics; Pediatrics</t>
+          <t>Medical Genetics; Endocrinology</t>
         </is>
       </c>
       <c r="L1075" t="inlineStr">
@@ -63421,7 +63421,7 @@
       </c>
       <c r="K1076" t="inlineStr">
         <is>
-          <t>Gastroenterology; Pediatrics</t>
+          <t>Pediatrics; Gastroenterology</t>
         </is>
       </c>
       <c r="L1076" t="inlineStr">
@@ -63537,7 +63537,7 @@
       </c>
       <c r="K1078" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Pediatrics</t>
+          <t>Pediatrics; Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L1078" t="inlineStr">
@@ -63769,7 +63769,7 @@
       </c>
       <c r="K1082" t="inlineStr">
         <is>
-          <t>Immunology and Rheumatology; Orthopedics and Traumatology</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L1082" t="inlineStr">
@@ -63943,7 +63943,7 @@
       </c>
       <c r="K1085" t="inlineStr">
         <is>
-          <t>Otorhinolaryngology; Oncology</t>
+          <t>Otorhinolaryngology</t>
         </is>
       </c>
       <c r="L1085" t="inlineStr">
@@ -64001,7 +64001,7 @@
       </c>
       <c r="K1086" t="inlineStr">
         <is>
-          <t>Oncology; Dermatology and Venereology</t>
+          <t>Dermatology and Venereology; Oncology</t>
         </is>
       </c>
       <c r="L1086" t="inlineStr">
@@ -64349,7 +64349,7 @@
       </c>
       <c r="K1092" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L1092" t="inlineStr">
@@ -64407,7 +64407,7 @@
       </c>
       <c r="K1093" t="inlineStr">
         <is>
-          <t>General Surgery; Orthopedics and Traumatology</t>
+          <t>Orthopedics and Traumatology; General Surgery</t>
         </is>
       </c>
       <c r="L1093" t="inlineStr">
@@ -65519,7 +65519,7 @@
       </c>
       <c r="K1112" t="inlineStr">
         <is>
-          <t>Hematology; Gastroenterology</t>
+          <t>Hematology</t>
         </is>
       </c>
       <c r="L1112" t="inlineStr">
@@ -66129,7 +66129,7 @@
       </c>
       <c r="K1122" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pediatrics</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L1122" t="inlineStr">
@@ -66187,7 +66187,7 @@
       </c>
       <c r="K1123" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L1123" t="inlineStr">
@@ -66709,7 +66709,7 @@
       </c>
       <c r="K1132" t="inlineStr">
         <is>
-          <t>General Surgery; Gastroenterology</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="L1132" t="inlineStr">
@@ -66941,7 +66941,7 @@
       </c>
       <c r="K1136" t="inlineStr">
         <is>
-          <t>General Surgery; Cardiology and Cardiac Surgery</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L1136" t="inlineStr">
@@ -67057,7 +67057,7 @@
       </c>
       <c r="K1138" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L1138" t="inlineStr">
@@ -67115,7 +67115,7 @@
       </c>
       <c r="K1139" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L1139" t="inlineStr">
@@ -67231,7 +67231,7 @@
       </c>
       <c r="K1141" t="inlineStr">
         <is>
-          <t>Gynecology and Obstetrics; Oncology</t>
+          <t>Gynecology and Obstetrics</t>
         </is>
       </c>
       <c r="L1141" t="inlineStr">
@@ -67879,7 +67879,7 @@
       </c>
       <c r="K1152" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L1152" t="inlineStr">
@@ -67937,7 +67937,7 @@
       </c>
       <c r="K1153" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Pediatrics</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L1153" t="inlineStr">
@@ -68373,7 +68373,7 @@
       </c>
       <c r="K1160" t="inlineStr">
         <is>
-          <t>Urology; Pharmacology and Toxicology</t>
+          <t>Urology</t>
         </is>
       </c>
       <c r="L1160" t="inlineStr">
@@ -68431,7 +68431,7 @@
       </c>
       <c r="K1161" t="inlineStr">
         <is>
-          <t>Urology; Medical Genetics</t>
+          <t>Urology; Oncology</t>
         </is>
       </c>
       <c r="L1161" t="inlineStr">
@@ -69341,7 +69341,7 @@
       </c>
       <c r="K1176" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery</t>
         </is>
       </c>
       <c r="L1176" t="inlineStr">
@@ -69631,7 +69631,7 @@
       </c>
       <c r="K1181" t="inlineStr">
         <is>
-          <t>Anesthesia and Intensive Care; Gynecology and Obstetrics</t>
+          <t>Anesthesia and Intensive Care; Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L1181" t="inlineStr">
@@ -69757,7 +69757,7 @@
       </c>
       <c r="K1183" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Infectious Diseases</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L1183" t="inlineStr">
@@ -69999,7 +69999,7 @@
       </c>
       <c r="K1187" t="inlineStr">
         <is>
-          <t>Infectious Diseases; Neurology and Neurosurgery</t>
+          <t>Neurology and Neurosurgery; Infectious Diseases</t>
         </is>
       </c>
       <c r="L1187" t="inlineStr">
@@ -70115,7 +70115,7 @@
       </c>
       <c r="K1189" t="inlineStr">
         <is>
-          <t>Cardiology and Cardiac Surgery; Anesthesia and Intensive Care</t>
+          <t>Anesthesia and Intensive Care</t>
         </is>
       </c>
       <c r="L1189" t="inlineStr">
@@ -70173,7 +70173,7 @@
       </c>
       <c r="K1190" t="inlineStr">
         <is>
-          <t>Neurology and Neurosurgery; Orthopedics and Traumatology</t>
+          <t>Neurology and Neurosurgery</t>
         </is>
       </c>
       <c r="L1190" t="inlineStr">
@@ -70231,7 +70231,7 @@
       </c>
       <c r="K1191" t="inlineStr">
         <is>
-          <t>Hematology; Pharmacology and Toxicology</t>
+          <t>Cardiology and Cardiac Surgery; Pharmacology and Toxicology</t>
         </is>
       </c>
       <c r="L1191" t="inlineStr">
@@ -71459,7 +71459,7 @@
       </c>
       <c r="K1212" t="inlineStr">
         <is>
-          <t>Medical Genetics; Immunology and Rheumatology</t>
+          <t>Medical Genetics</t>
         </is>
       </c>
       <c r="L1212" t="inlineStr">
@@ -72745,7 +72745,7 @@
       </c>
       <c r="K1234" t="inlineStr">
         <is>
-          <t>Pulmonology and Thoracic Surgery; Anesthesia and Intensive Care</t>
+          <t>Pulmonology and Thoracic Surgery</t>
         </is>
       </c>
       <c r="L1234" t="inlineStr">
@@ -72977,7 +72977,7 @@
       </c>
       <c r="K1238" t="inlineStr">
         <is>
-          <t>Endocrinology; Pharmacology and Toxicology</t>
+          <t>Endocrinology</t>
         </is>
       </c>
       <c r="L1238" t="inlineStr">
@@ -73325,7 +73325,7 @@
       </c>
       <c r="K1244" t="inlineStr">
         <is>
-          <t>Occupational Medicine; Otorhinolaryngology</t>
+          <t>Occupational Medicine</t>
         </is>
       </c>
       <c r="L1244" t="inlineStr">
@@ -73789,7 +73789,7 @@
       </c>
       <c r="K1252" t="inlineStr">
         <is>
-          <t>Gastroenterology; Hematology</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
       <c r="L1252" t="inlineStr">
@@ -73905,7 +73905,7 @@
       </c>
       <c r="K1254" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L1254" t="inlineStr">
@@ -73963,7 +73963,7 @@
       </c>
       <c r="K1255" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Gastroenterology</t>
+          <t>Gastroenterology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L1255" t="inlineStr">
@@ -74021,7 +74021,7 @@
       </c>
       <c r="K1256" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging and Nuclear Medicine; Oncology</t>
+          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
         </is>
       </c>
       <c r="L1256" t="inlineStr">
@@ -74079,7 +74079,7 @@
       </c>
       <c r="K1257" t="inlineStr">
         <is>
-          <t>Orthopedics and Traumatology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Orthopedics and Traumatology</t>
         </is>
       </c>
       <c r="L1257" t="inlineStr">
@@ -74263,7 +74263,7 @@
       </c>
       <c r="K1260" t="inlineStr">
         <is>
-          <t>Oncology; Diagnostic Imaging and Nuclear Medicine</t>
+          <t>Oncology</t>
         </is>
       </c>
       <c r="L1260" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_complete_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_complete_EN.xlsx
@@ -40089,7 +40089,7 @@
       </c>
       <c r="M677" t="inlineStr">
         <is>
-          <t>Brain CT Scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="N677" t="inlineStr">
@@ -65955,7 +65955,7 @@
       </c>
       <c r="M1119" t="inlineStr">
         <is>
-          <t>Brain TC scan</t>
+          <t>Brain CT scan</t>
         </is>
       </c>
       <c r="N1119" t="inlineStr">

--- a/Dataset/EN/xlsx/ITAMed_complete_EN.xlsx
+++ b/Dataset/EN/xlsx/ITAMed_complete_EN.xlsx
@@ -53645,7 +53645,7 @@
       </c>
       <c r="M909" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endoscopic image </t>
+          <t>Endoscopic image</t>
         </is>
       </c>
       <c r="N909" t="inlineStr">
